--- a/originales/respuestas/2025/01. Calificadas/root/Alcaldía Local De Puente Aranda.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/root/Alcaldía Local De Puente Aranda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Personal\Desktop\Respuesta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50F0329-3FDB-47EC-AD41-DA327BC17EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9949CE8B-0941-4011-9A08-E731989122D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="4" xr2:uid="{855A3163-777B-47BE-994C-4C6D1A1E0D44}"/>
+    <workbookView xWindow="3075" yWindow="0" windowWidth="23040" windowHeight="15480" activeTab="4" xr2:uid="{855A3163-777B-47BE-994C-4C6D1A1E0D44}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1217,11 +1217,11 @@
       </c>
       <c r="J2" s="6"/>
       <c r="K2" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N2" s="6"/>
       <c r="O2" s="6">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="P2" s="6"/>
       <c r="Q2" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
@@ -1276,11 +1276,11 @@
       </c>
       <c r="J3" s="9"/>
       <c r="K3" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L3" s="9"/>
       <c r="M3" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N3" s="9"/>
       <c r="O3" s="9">
@@ -2379,15 +2379,15 @@
       </c>
       <c r="J22" s="6"/>
       <c r="K22" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L22" s="6"/>
       <c r="M22" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N22" s="6"/>
       <c r="O22" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
@@ -2436,15 +2436,15 @@
       </c>
       <c r="J23" s="6"/>
       <c r="K23" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L23" s="6"/>
       <c r="M23" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N23" s="6"/>
       <c r="O23" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P23" s="6"/>
       <c r="Q23" s="6"/>
@@ -2493,19 +2493,19 @@
       </c>
       <c r="J24" s="6"/>
       <c r="K24" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L24" s="6"/>
       <c r="M24" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N24" s="6"/>
       <c r="O24" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P24" s="6"/>
       <c r="Q24" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R24" s="6"/>
       <c r="S24" s="6"/>
@@ -2552,19 +2552,19 @@
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L25" s="9"/>
       <c r="M25" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N25" s="9"/>
       <c r="O25" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P25" s="9"/>
       <c r="Q25" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R25" s="9"/>
       <c r="S25" s="9"/>
@@ -2615,11 +2615,11 @@
       </c>
       <c r="L26" s="9"/>
       <c r="M26" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N26" s="9"/>
       <c r="O26" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P26" s="9"/>
       <c r="Q26" s="9">
@@ -2869,11 +2869,11 @@
       </c>
       <c r="L3" s="15"/>
       <c r="M3" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N3" s="9"/>
       <c r="O3" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P3" s="9"/>
       <c r="Q3" s="9">
@@ -2912,19 +2912,19 @@
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L4" s="13"/>
       <c r="M4" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4" s="6"/>
       <c r="O4" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P4" s="6"/>
       <c r="Q4" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4" s="6"/>
       <c r="S4" s="14"/>
@@ -3057,23 +3057,23 @@
       </c>
       <c r="J7" s="9"/>
       <c r="K7" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L7" s="15"/>
       <c r="M7" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N7" s="9"/>
       <c r="O7" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P7" s="9"/>
       <c r="Q7" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R7" s="9"/>
       <c r="S7" s="16">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="126.75" customHeight="1">
@@ -3106,23 +3106,23 @@
       </c>
       <c r="J8" s="9"/>
       <c r="K8" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L8" s="15"/>
       <c r="M8" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N8" s="9"/>
       <c r="O8" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P8" s="9"/>
       <c r="Q8" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R8" s="9"/>
       <c r="S8" s="16">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="126.75" customHeight="1">
@@ -3155,23 +3155,23 @@
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L9" s="15"/>
       <c r="M9" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N9" s="9"/>
       <c r="O9" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P9" s="9"/>
       <c r="Q9" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R9" s="9"/>
       <c r="S9" s="16">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="126.75" customHeight="1">
@@ -3204,23 +3204,23 @@
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L10" s="15"/>
       <c r="M10" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N10" s="9"/>
       <c r="O10" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P10" s="9"/>
       <c r="Q10" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R10" s="9"/>
       <c r="S10" s="16">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="126.75" customHeight="1">
@@ -3253,23 +3253,23 @@
       </c>
       <c r="J11" s="9"/>
       <c r="K11" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L11" s="15"/>
       <c r="M11" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N11" s="9"/>
       <c r="O11" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P11" s="9"/>
       <c r="Q11" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R11" s="9"/>
       <c r="S11" s="16">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="126.75" customHeight="1">
@@ -3302,15 +3302,15 @@
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N12" s="6"/>
       <c r="O12" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="R12" s="6"/>
       <c r="S12" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="126.75" customHeight="1">
@@ -3351,15 +3351,15 @@
       </c>
       <c r="J13" s="9"/>
       <c r="K13" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L13" s="15"/>
       <c r="M13" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N13" s="9"/>
       <c r="O13" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P13" s="9"/>
       <c r="Q13" s="9">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="L14" s="15"/>
       <c r="M14" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N14" s="9"/>
       <c r="O14" s="9">
@@ -3449,11 +3449,11 @@
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N15" s="6"/>
       <c r="O15" s="6">
@@ -3461,11 +3461,11 @@
       </c>
       <c r="P15" s="6"/>
       <c r="Q15" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R15" s="6"/>
       <c r="S15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="126.75" customHeight="1">
@@ -3498,23 +3498,23 @@
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N16" s="6"/>
       <c r="O16" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R16" s="6"/>
       <c r="S16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="126.75" customHeight="1">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N17" s="6"/>
       <c r="O17" s="6">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="J18" s="6"/>
       <c r="K18" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L18" s="13"/>
       <c r="M18" s="6">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="N18" s="6"/>
       <c r="O18" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P18" s="6"/>
       <c r="Q18" s="6">
@@ -3631,11 +3631,11 @@
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L19" s="15"/>
       <c r="M19" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N19" s="9"/>
       <c r="O19" s="9">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="P19" s="9"/>
       <c r="Q19" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R19" s="9"/>
       <c r="S19" s="16">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L20" s="13"/>
       <c r="M20" s="6">
@@ -3688,11 +3688,11 @@
       </c>
       <c r="N20" s="6"/>
       <c r="O20" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R20" s="6"/>
       <c r="S20" s="14"/>
@@ -3852,23 +3852,23 @@
       </c>
       <c r="J3" s="14"/>
       <c r="K3" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L3" s="14"/>
       <c r="M3" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N3" s="14"/>
       <c r="O3" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P3" s="14"/>
       <c r="Q3" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R3" s="14"/>
       <c r="S3" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="126.75" customHeight="1">
@@ -3897,23 +3897,23 @@
       </c>
       <c r="J4" s="16"/>
       <c r="K4" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L4" s="14"/>
       <c r="M4" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4" s="14"/>
       <c r="O4" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P4" s="14"/>
       <c r="Q4" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4" s="14"/>
       <c r="S4" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -4031,19 +4031,19 @@
       </c>
       <c r="J2" s="14"/>
       <c r="K2" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L2" s="17"/>
       <c r="M2" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N2" s="14"/>
       <c r="O2" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P2" s="14"/>
       <c r="Q2" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R2" s="14"/>
       <c r="S2" s="14"/>
@@ -4074,23 +4074,23 @@
       </c>
       <c r="J3" s="14"/>
       <c r="K3" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L3" s="17"/>
       <c r="M3" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N3" s="14"/>
       <c r="O3" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P3" s="14"/>
       <c r="Q3" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R3" s="14"/>
       <c r="S3" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="126.75" customHeight="1">
@@ -4119,23 +4119,23 @@
       </c>
       <c r="J4" s="16"/>
       <c r="K4" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L4" s="17"/>
       <c r="M4" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4" s="14"/>
       <c r="O4" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P4" s="14"/>
       <c r="Q4" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4" s="14"/>
       <c r="S4" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="126.75" customHeight="1">
@@ -4166,19 +4166,19 @@
       </c>
       <c r="J5" s="16"/>
       <c r="K5" s="16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L5" s="19"/>
       <c r="M5" s="16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N5" s="16"/>
       <c r="O5" s="16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R5" s="16"/>
       <c r="S5" s="16">
@@ -4211,19 +4211,19 @@
       </c>
       <c r="J6" s="16"/>
       <c r="K6" s="16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L6" s="19"/>
       <c r="M6" s="16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N6" s="16"/>
       <c r="O6" s="16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P6" s="16"/>
       <c r="Q6" s="16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R6" s="16"/>
       <c r="S6" s="16">
@@ -4258,23 +4258,23 @@
       </c>
       <c r="J7" s="14"/>
       <c r="K7" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L7" s="17"/>
       <c r="M7" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N7" s="14"/>
       <c r="O7" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P7" s="14"/>
       <c r="Q7" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R7" s="14"/>
       <c r="S7" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="126.75" customHeight="1">
@@ -4303,23 +4303,23 @@
       </c>
       <c r="J8" s="16"/>
       <c r="K8" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L8" s="17"/>
       <c r="M8" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N8" s="14"/>
       <c r="O8" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P8" s="14"/>
       <c r="Q8" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R8" s="14"/>
       <c r="S8" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="126.75" customHeight="1">

--- a/originales/respuestas/2025/01. Calificadas/root/Alcaldía Local De Puente Aranda.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/root/Alcaldía Local De Puente Aranda.xlsx
@@ -1,28 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Personal\Desktop\Respuesta\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9949CE8B-0941-4011-9A08-E731989122D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="3075" yWindow="0" windowWidth="23040" windowHeight="15480" activeTab="4" xr2:uid="{855A3163-777B-47BE-994C-4C6D1A1E0D44}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="C1" sheetId="2" r:id="rId2"/>
-    <sheet name="C2" sheetId="3" r:id="rId3"/>
-    <sheet name="C3" sheetId="4" r:id="rId4"/>
-    <sheet name="C4" sheetId="5" r:id="rId5"/>
+    <sheet state="visible" name="Hoja1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="C1" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="C2" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="C3" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="C4" sheetId="5" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="568YOSRjzHf0GfdwkiOr3C0fLhk7IziwC4hITw/voa8="/>
     </ext>
   </extLst>
 </workbook>
@@ -141,11 +132,10 @@
   <si>
     <r>
       <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF1155CC"/>
+        <sz val="11.0"/>
         <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>acuerdolocalno.025de2023 (1).pdf</t>
     </r>
@@ -177,11 +167,10 @@
   <si>
     <r>
       <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF1155CC"/>
+        <sz val="11.0"/>
         <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>ejecución presupuestal 2024.pdf</t>
     </r>
@@ -201,11 +190,10 @@
   <si>
     <r>
       <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF1155CC"/>
+        <sz val="11.0"/>
         <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>acuerdolocalno.025de2023 (2).pdf</t>
     </r>
@@ -449,7 +437,7 @@
     <t>¿Su entidad ha puesto a disposición de todos formación orientada al fortalecimiento de capacidades en innovación?</t>
   </si>
   <si>
-    <t>Pregunta 30</t>
+    <t>Pregunta 30.</t>
   </si>
   <si>
     <t>¿Qué estrategias o iniciativas ha implementado su entidad para fomentar una cultura de innovación entre sus funcionarios y contratistas?</t>
@@ -458,7 +446,7 @@
     <t>Programas de sensibilización sobre innovación pública., Espacios de ideación y cocreación con los equipos internos., Procesos de formación o capacitaciones en metodologías de innovación., Creación de equipos o laboratorios de innovación internos., Otras (especifique).</t>
   </si>
   <si>
-    <t>Pregunta 31</t>
+    <t>Pregunta 31.</t>
   </si>
   <si>
     <t>¿De qué manera ha incentivado su entidad la participación de los funcionarios y contratistas en procesos de innovación?</t>
@@ -506,10 +494,10 @@
   <si>
     <r>
       <rPr>
+        <rFont val="Calibri, sans-serif"/>
+        <color rgb="FF1155CC"/>
+        <sz val="11.0"/>
         <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri, sans-serif"/>
       </rPr>
       <t>Captura de pantalla 2024-05-14 a la(s) 1.38.06ÔÇ»p.┬ám. (1).pdf</t>
     </r>
@@ -541,11 +529,10 @@
   <si>
     <r>
       <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF1155CC"/>
+        <sz val="11.0"/>
         <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>4. Informe de resultados Gestion del Objetivo 4 CO╠üDIGO FUENTE COPIA APP DEL SERVIDOR SEPTIEMBRE.docx</t>
     </r>
@@ -560,6 +547,9 @@
     <t>Número de participantes en eventos de difusión., Cantidad de documentos o publicaciones generadas., Aplicación del conocimiento en nuevas iniciativas de innovación.</t>
   </si>
   <si>
+    <t>enlace pregunta 37.txt</t>
+  </si>
+  <si>
     <t>Pregunta 38.</t>
   </si>
   <si>
@@ -573,11 +563,10 @@
   <si>
     <r>
       <rPr>
+        <rFont val="Calibri"/>
+        <color rgb="FF1155CC"/>
+        <sz val="11.0"/>
         <u/>
-        <sz val="11"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
       </rPr>
       <t>publicaciojnes blog PUENTE LAB Puente Aranda App.pdf</t>
     </r>
@@ -599,48 +588,47 @@
   </si>
   <si>
     <t>¿Su entidad desarrolló algún instrumento para hacer monitoreo y seguimiento a las innovaciones implementadas?</t>
-  </si>
-  <si>
-    <t>enlace pregunta 37.txt</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="6">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
-      <color rgb="FF1155CC"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
       <color rgb="FF1155CC"/>
-      <name val="Calibri, sans-serif"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="5">
@@ -648,7 +636,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -669,14 +657,8 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="5">
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FFFFFFFF"/>
@@ -690,7 +672,6 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -705,7 +686,6 @@
       <bottom style="thin">
         <color rgb="FF284E3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -720,106 +700,130 @@
       <bottom style="thin">
         <color rgb="FF284E3F"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+  <cellXfs count="23">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf borderId="3" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf borderId="4" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="4472C4"/>
@@ -843,113 +847,19 @@
         <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="0563C1"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1090,33 +1000,1018 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9F854B1-02CB-4E16-8FE8-6DCA21E90366}">
-  <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="26" width="10.71"/>
+  </cols>
+  <sheetData>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+  </sheetData>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA9DBC66-E041-4D60-9146-D15FE5173D98}">
-  <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:AE27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="31" width="10.71"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="43.5" customHeight="1">
+    <row r="1" ht="43.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1187,15 +2082,15 @@
       <c r="AD1" s="5"/>
       <c r="AE1" s="5"/>
     </row>
-    <row r="2" spans="1:31" ht="126.75" customHeight="1">
+    <row r="2" ht="126.75" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B2" s="6">
-        <v>13</v>
+        <v>13.0</v>
       </c>
       <c r="C2" s="7">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>20</v>
@@ -1217,19 +2112,19 @@
       </c>
       <c r="J2" s="6"/>
       <c r="K2" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N2" s="6"/>
       <c r="O2" s="6">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="P2" s="6"/>
       <c r="Q2" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R2" s="6"/>
       <c r="S2" s="6"/>
@@ -1246,15 +2141,15 @@
       <c r="AD2" s="8"/>
       <c r="AE2" s="8"/>
     </row>
-    <row r="3" spans="1:31" ht="126.75" customHeight="1">
+    <row r="3" ht="126.75" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="9">
-        <v>14</v>
+        <v>14.0</v>
       </c>
       <c r="C3" s="10">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>26</v>
@@ -1276,19 +2171,19 @@
       </c>
       <c r="J3" s="9"/>
       <c r="K3" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L3" s="9"/>
       <c r="M3" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N3" s="9"/>
       <c r="O3" s="9">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="P3" s="9"/>
       <c r="Q3" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R3" s="9"/>
       <c r="S3" s="9"/>
@@ -1305,15 +2200,15 @@
       <c r="AD3" s="8"/>
       <c r="AE3" s="8"/>
     </row>
-    <row r="4" spans="1:31" ht="126.75" customHeight="1">
+    <row r="4" ht="126.75" customHeight="1">
       <c r="A4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="6">
-        <v>38</v>
+        <v>38.0</v>
       </c>
       <c r="C4" s="7">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>28</v>
@@ -1331,19 +2226,19 @@
         <v>31</v>
       </c>
       <c r="I4" s="6">
-        <v>2926199000</v>
+        <v>2.926199E9</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L4" s="6"/>
       <c r="M4" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N4" s="6"/>
       <c r="O4" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
@@ -1362,15 +2257,15 @@
       <c r="AD4" s="8"/>
       <c r="AE4" s="8"/>
     </row>
-    <row r="5" spans="1:31" ht="126.75" customHeight="1">
+    <row r="5" ht="126.75" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B5" s="6">
-        <v>39</v>
+        <v>39.0</v>
       </c>
       <c r="C5" s="7">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>28</v>
@@ -1388,19 +2283,19 @@
         <v>33</v>
       </c>
       <c r="I5" s="6">
-        <v>3414018000</v>
+        <v>3.414018E9</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
@@ -1419,13 +2314,13 @@
       <c r="AD5" s="8"/>
       <c r="AE5" s="8"/>
     </row>
-    <row r="6" spans="1:31" ht="126.75" customHeight="1">
+    <row r="6" ht="126.75" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="10">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>28</v>
@@ -1445,15 +2340,15 @@
       </c>
       <c r="J6" s="9"/>
       <c r="K6" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N6" s="6"/>
       <c r="O6" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P6" s="9"/>
       <c r="Q6" s="9"/>
@@ -1472,15 +2367,15 @@
       <c r="AD6" s="8"/>
       <c r="AE6" s="8"/>
     </row>
-    <row r="7" spans="1:31" ht="126.75" customHeight="1">
+    <row r="7" ht="126.75" customHeight="1">
       <c r="A7" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="6">
-        <v>41</v>
+        <v>41.0</v>
       </c>
       <c r="C7" s="7">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>37</v>
@@ -1498,27 +2393,27 @@
         <v>33</v>
       </c>
       <c r="I7" s="6">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="L7" s="6"/>
       <c r="M7" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="N7" s="6"/>
       <c r="O7" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="P7" s="6"/>
       <c r="Q7" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="R7" s="6"/>
       <c r="S7" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="T7" s="8"/>
       <c r="U7" s="8"/>
@@ -1533,15 +2428,15 @@
       <c r="AD7" s="8"/>
       <c r="AE7" s="8"/>
     </row>
-    <row r="8" spans="1:31" ht="126.75" customHeight="1">
+    <row r="8" ht="126.75" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="9">
-        <v>42</v>
+        <v>42.0</v>
       </c>
       <c r="C8" s="10">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>37</v>
@@ -1563,23 +2458,23 @@
       </c>
       <c r="J8" s="9"/>
       <c r="K8" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="L8" s="6"/>
       <c r="M8" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="N8" s="6"/>
       <c r="O8" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="P8" s="6"/>
       <c r="Q8" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="R8" s="6"/>
       <c r="S8" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="T8" s="8"/>
       <c r="U8" s="8"/>
@@ -1594,15 +2489,15 @@
       <c r="AD8" s="8"/>
       <c r="AE8" s="8"/>
     </row>
-    <row r="9" spans="1:31" ht="126.75" customHeight="1">
+    <row r="9" ht="126.75" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="9">
-        <v>43</v>
+        <v>43.0</v>
       </c>
       <c r="C9" s="10">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>37</v>
@@ -1620,27 +2515,27 @@
         <v>33</v>
       </c>
       <c r="I9" s="9">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="J9" s="9"/>
       <c r="K9" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="L9" s="6"/>
       <c r="M9" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="N9" s="6"/>
       <c r="O9" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="P9" s="6"/>
       <c r="Q9" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="R9" s="6"/>
       <c r="S9" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="T9" s="8"/>
       <c r="U9" s="8"/>
@@ -1655,13 +2550,13 @@
       <c r="AD9" s="8"/>
       <c r="AE9" s="8"/>
     </row>
-    <row r="10" spans="1:31" ht="126.75" customHeight="1">
+    <row r="10" ht="126.75" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="10">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>37</v>
@@ -1679,23 +2574,23 @@
       </c>
       <c r="J10" s="9"/>
       <c r="K10" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="N10" s="6"/>
       <c r="O10" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="P10" s="6"/>
       <c r="Q10" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="R10" s="6"/>
       <c r="S10" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="T10" s="8"/>
       <c r="U10" s="8"/>
@@ -1710,15 +2605,15 @@
       <c r="AD10" s="8"/>
       <c r="AE10" s="8"/>
     </row>
-    <row r="11" spans="1:31" ht="126.75" customHeight="1">
+    <row r="11" ht="126.75" customHeight="1">
       <c r="A11" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="9">
-        <v>48</v>
+        <v>48.0</v>
       </c>
       <c r="C11" s="10">
-        <v>11</v>
+        <v>11.0</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>46</v>
@@ -1736,19 +2631,19 @@
         <v>33</v>
       </c>
       <c r="I11" s="9">
-        <v>73258398000</v>
+        <v>7.3258398E10</v>
       </c>
       <c r="J11" s="9"/>
       <c r="K11" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L11" s="9"/>
       <c r="M11" s="9">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="N11" s="9"/>
       <c r="O11" s="9">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="P11" s="9"/>
       <c r="Q11" s="9"/>
@@ -1767,15 +2662,15 @@
       <c r="AD11" s="8"/>
       <c r="AE11" s="8"/>
     </row>
-    <row r="12" spans="1:31" ht="126.75" customHeight="1">
+    <row r="12" ht="126.75" customHeight="1">
       <c r="A12" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="6">
-        <v>49</v>
+        <v>49.0</v>
       </c>
       <c r="C12" s="7">
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>46</v>
@@ -1793,19 +2688,19 @@
         <v>33</v>
       </c>
       <c r="I12" s="6">
-        <v>81417427000</v>
+        <v>8.1417427E10</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L12" s="9"/>
       <c r="M12" s="9">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="N12" s="9"/>
       <c r="O12" s="9">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6"/>
@@ -1824,13 +2719,13 @@
       <c r="AD12" s="8"/>
       <c r="AE12" s="8"/>
     </row>
-    <row r="13" spans="1:31" ht="126.75" customHeight="1">
+    <row r="13" ht="126.75" customHeight="1">
       <c r="A13" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="7">
-        <v>13</v>
+        <v>13.0</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>46</v>
@@ -1848,15 +2743,15 @@
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L13" s="9"/>
       <c r="M13" s="9">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="N13" s="9"/>
       <c r="O13" s="9">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="P13" s="6"/>
       <c r="Q13" s="6"/>
@@ -1875,15 +2770,15 @@
       <c r="AD13" s="8"/>
       <c r="AE13" s="8"/>
     </row>
-    <row r="14" spans="1:31" ht="126.75" customHeight="1">
+    <row r="14" ht="126.75" customHeight="1">
       <c r="A14" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B14" s="9">
-        <v>42</v>
+        <v>42.0</v>
       </c>
       <c r="C14" s="10">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>51</v>
@@ -1905,23 +2800,23 @@
       </c>
       <c r="J14" s="9"/>
       <c r="K14" s="9">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="L14" s="9"/>
       <c r="M14" s="9">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="N14" s="9"/>
       <c r="O14" s="9">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="P14" s="9"/>
       <c r="Q14" s="9">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="R14" s="9"/>
       <c r="S14" s="9">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="T14" s="8"/>
       <c r="U14" s="8"/>
@@ -1936,15 +2831,15 @@
       <c r="AD14" s="8"/>
       <c r="AE14" s="8"/>
     </row>
-    <row r="15" spans="1:31" ht="126.75" customHeight="1">
+    <row r="15" ht="126.75" customHeight="1">
       <c r="A15" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="9">
-        <v>44</v>
+        <v>44.0</v>
       </c>
       <c r="C15" s="10">
-        <v>16</v>
+        <v>16.0</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>51</v>
@@ -1966,23 +2861,23 @@
       </c>
       <c r="J15" s="9"/>
       <c r="K15" s="9">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="L15" s="9"/>
       <c r="M15" s="9">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="N15" s="9"/>
       <c r="O15" s="9">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="P15" s="9"/>
       <c r="Q15" s="9">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="R15" s="9"/>
       <c r="S15" s="9">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="T15" s="8"/>
       <c r="U15" s="8"/>
@@ -1997,15 +2892,15 @@
       <c r="AD15" s="8"/>
       <c r="AE15" s="8"/>
     </row>
-    <row r="16" spans="1:31" ht="126.75" customHeight="1">
+    <row r="16" ht="126.75" customHeight="1">
       <c r="A16" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B16" s="6">
-        <v>39</v>
+        <v>39.0</v>
       </c>
       <c r="C16" s="7">
-        <v>17</v>
+        <v>17.0</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>51</v>
@@ -2023,27 +2918,27 @@
         <v>33</v>
       </c>
       <c r="I16" s="6">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="9">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="L16" s="9"/>
       <c r="M16" s="9">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="N16" s="9"/>
       <c r="O16" s="9">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="P16" s="9"/>
       <c r="Q16" s="9">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="R16" s="9"/>
       <c r="S16" s="9">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="T16" s="8"/>
       <c r="U16" s="8"/>
@@ -2058,15 +2953,15 @@
       <c r="AD16" s="8"/>
       <c r="AE16" s="8"/>
     </row>
-    <row r="17" spans="1:31" ht="126.75" customHeight="1">
+    <row r="17" ht="126.75" customHeight="1">
       <c r="A17" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="9">
-        <v>58</v>
+        <v>58.0</v>
       </c>
       <c r="C17" s="10">
-        <v>19</v>
+        <v>19.0</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>56</v>
@@ -2084,19 +2979,19 @@
         <v>33</v>
       </c>
       <c r="I17" s="9">
-        <v>36</v>
+        <v>36.0</v>
       </c>
       <c r="J17" s="9"/>
       <c r="K17" s="9">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="L17" s="9"/>
       <c r="M17" s="9">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="N17" s="9"/>
       <c r="O17" s="9">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="P17" s="9"/>
       <c r="Q17" s="9"/>
@@ -2115,15 +3010,15 @@
       <c r="AD17" s="8"/>
       <c r="AE17" s="8"/>
     </row>
-    <row r="18" spans="1:31" ht="126.75" customHeight="1">
+    <row r="18" ht="126.75" customHeight="1">
       <c r="A18" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="9">
-        <v>59</v>
+        <v>59.0</v>
       </c>
       <c r="C18" s="10">
-        <v>20</v>
+        <v>20.0</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>56</v>
@@ -2141,19 +3036,19 @@
         <v>33</v>
       </c>
       <c r="I18" s="9">
-        <v>36</v>
+        <v>36.0</v>
       </c>
       <c r="J18" s="9"/>
       <c r="K18" s="9">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="L18" s="9"/>
       <c r="M18" s="9">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="N18" s="9"/>
       <c r="O18" s="9">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="P18" s="9"/>
       <c r="Q18" s="9"/>
@@ -2172,15 +3067,15 @@
       <c r="AD18" s="8"/>
       <c r="AE18" s="8"/>
     </row>
-    <row r="19" spans="1:31" ht="126.75" customHeight="1">
+    <row r="19" ht="126.75" customHeight="1">
       <c r="A19" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="6">
-        <v>60</v>
+        <v>60.0</v>
       </c>
       <c r="C19" s="7">
-        <v>21</v>
+        <v>21.0</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>60</v>
@@ -2198,23 +3093,23 @@
         <v>33</v>
       </c>
       <c r="I19" s="6">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="J19" s="6"/>
       <c r="K19" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="L19" s="6"/>
       <c r="M19" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="N19" s="6"/>
       <c r="O19" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="P19" s="6"/>
       <c r="Q19" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
@@ -2231,15 +3126,15 @@
       <c r="AD19" s="8"/>
       <c r="AE19" s="8"/>
     </row>
-    <row r="20" spans="1:31" ht="126.75" customHeight="1">
+    <row r="20" ht="126.75" customHeight="1">
       <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="6">
-        <v>61</v>
+        <v>61.0</v>
       </c>
       <c r="C20" s="7">
-        <v>22</v>
+        <v>22.0</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>60</v>
@@ -2257,23 +3152,23 @@
         <v>33</v>
       </c>
       <c r="I20" s="6">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="L20" s="6"/>
       <c r="M20" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="N20" s="6"/>
       <c r="O20" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="R20" s="6"/>
       <c r="S20" s="6"/>
@@ -2290,15 +3185,15 @@
       <c r="AD20" s="8"/>
       <c r="AE20" s="8"/>
     </row>
-    <row r="21" spans="1:31" ht="126.75" customHeight="1">
+    <row r="21" ht="126.75" customHeight="1">
       <c r="A21" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="6">
-        <v>62</v>
+        <v>62.0</v>
       </c>
       <c r="C21" s="7">
-        <v>23</v>
+        <v>23.0</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>60</v>
@@ -2320,19 +3215,19 @@
       </c>
       <c r="J21" s="6"/>
       <c r="K21" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="L21" s="6"/>
       <c r="M21" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="N21" s="6"/>
       <c r="O21" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="P21" s="6"/>
       <c r="Q21" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="R21" s="6"/>
       <c r="S21" s="6"/>
@@ -2349,15 +3244,15 @@
       <c r="AD21" s="8"/>
       <c r="AE21" s="8"/>
     </row>
-    <row r="22" spans="1:31" ht="126.75" customHeight="1">
+    <row r="22" ht="126.75" customHeight="1">
       <c r="A22" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B22" s="6">
-        <v>64</v>
+        <v>64.0</v>
       </c>
       <c r="C22" s="7">
-        <v>24</v>
+        <v>24.0</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>65</v>
@@ -2375,19 +3270,19 @@
         <v>33</v>
       </c>
       <c r="I22" s="6">
-        <v>373</v>
+        <v>373.0</v>
       </c>
       <c r="J22" s="6"/>
       <c r="K22" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L22" s="6"/>
       <c r="M22" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N22" s="6"/>
       <c r="O22" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
@@ -2406,15 +3301,15 @@
       <c r="AD22" s="8"/>
       <c r="AE22" s="8"/>
     </row>
-    <row r="23" spans="1:31" ht="126.75" customHeight="1">
+    <row r="23" ht="126.75" customHeight="1">
       <c r="A23" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B23" s="6">
-        <v>65</v>
+        <v>65.0</v>
       </c>
       <c r="C23" s="7">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>65</v>
@@ -2432,19 +3327,19 @@
         <v>33</v>
       </c>
       <c r="I23" s="6">
-        <v>793</v>
+        <v>793.0</v>
       </c>
       <c r="J23" s="6"/>
       <c r="K23" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L23" s="6"/>
       <c r="M23" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N23" s="6"/>
       <c r="O23" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P23" s="6"/>
       <c r="Q23" s="6"/>
@@ -2463,15 +3358,15 @@
       <c r="AD23" s="8"/>
       <c r="AE23" s="8"/>
     </row>
-    <row r="24" spans="1:31" ht="126.75" customHeight="1">
+    <row r="24" ht="126.75" customHeight="1">
       <c r="A24" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B24" s="6">
-        <v>69</v>
+        <v>69.0</v>
       </c>
       <c r="C24" s="7">
-        <v>27</v>
+        <v>27.0</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>68</v>
@@ -2489,23 +3384,23 @@
         <v>33</v>
       </c>
       <c r="I24" s="6">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="J24" s="6"/>
       <c r="K24" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L24" s="6"/>
       <c r="M24" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N24" s="6"/>
       <c r="O24" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P24" s="6"/>
       <c r="Q24" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R24" s="6"/>
       <c r="S24" s="6"/>
@@ -2522,15 +3417,15 @@
       <c r="AD24" s="8"/>
       <c r="AE24" s="8"/>
     </row>
-    <row r="25" spans="1:31" ht="126.75" customHeight="1">
+    <row r="25" ht="126.75" customHeight="1">
       <c r="A25" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B25" s="9">
-        <v>23</v>
+        <v>23.0</v>
       </c>
       <c r="C25" s="10">
-        <v>29</v>
+        <v>29.0</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>70</v>
@@ -2552,19 +3447,19 @@
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L25" s="9"/>
       <c r="M25" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N25" s="9"/>
       <c r="O25" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P25" s="9"/>
       <c r="Q25" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R25" s="9"/>
       <c r="S25" s="9"/>
@@ -2581,15 +3476,15 @@
       <c r="AD25" s="8"/>
       <c r="AE25" s="8"/>
     </row>
-    <row r="26" spans="1:31" ht="126.75" customHeight="1">
+    <row r="26" ht="126.75" customHeight="1">
       <c r="A26" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B26" s="9">
-        <v>25</v>
+        <v>25.0</v>
       </c>
       <c r="C26" s="10">
-        <v>30</v>
+        <v>30.0</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>73</v>
@@ -2611,19 +3506,19 @@
       </c>
       <c r="J26" s="9"/>
       <c r="K26" s="9">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="L26" s="9"/>
       <c r="M26" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N26" s="9"/>
       <c r="O26" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P26" s="9"/>
       <c r="Q26" s="9">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="R26" s="9"/>
       <c r="S26" s="9"/>
@@ -2640,15 +3535,15 @@
       <c r="AD26" s="8"/>
       <c r="AE26" s="8"/>
     </row>
-    <row r="27" spans="1:31" ht="126.75" customHeight="1">
+    <row r="27" ht="126.75" customHeight="1">
       <c r="A27" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B27" s="6">
-        <v>27</v>
+        <v>27.0</v>
       </c>
       <c r="C27" s="7">
-        <v>31</v>
+        <v>31.0</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>75</v>
@@ -2670,23 +3565,23 @@
       </c>
       <c r="J27" s="6"/>
       <c r="K27" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="L27" s="6"/>
       <c r="M27" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="N27" s="6"/>
       <c r="O27" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="P27" s="6"/>
       <c r="Q27" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="R27" s="6"/>
       <c r="S27" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="T27" s="8"/>
       <c r="U27" s="8"/>
@@ -2701,23 +3596,1003 @@
       <c r="AD27" s="8"/>
       <c r="AE27" s="8"/>
     </row>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I6" r:id="rId1" xr:uid="{AC7EEC32-A148-47D0-9759-E152E6C10E93}"/>
-    <hyperlink ref="I10" r:id="rId2" xr:uid="{9922FD5B-FFA9-4C09-9F80-606FB7341874}"/>
-    <hyperlink ref="I13" r:id="rId3" xr:uid="{D2882166-5D3A-43D8-9DDD-8A343D04018D}"/>
+    <hyperlink r:id="rId1" ref="I6"/>
+    <hyperlink r:id="rId2" ref="I10"/>
+    <hyperlink r:id="rId3" ref="I13"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E083DA3-557C-48AD-833E-0B8F215A88CD}">
-  <sheetPr codeName="Hoja3"/>
-  <dimension ref="A1:AE20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="31" width="10.71"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="43.5" customHeight="1">
+    <row r="1" ht="43.5" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2788,15 +4663,15 @@
       <c r="AD1" s="5"/>
       <c r="AE1" s="5"/>
     </row>
-    <row r="2" spans="1:31" ht="126.75" customHeight="1">
+    <row r="2" ht="126.75" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B2" s="6">
-        <v>88</v>
+        <v>88.0</v>
       </c>
       <c r="C2" s="7">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>79</v>
@@ -2818,32 +4693,32 @@
       </c>
       <c r="J2" s="6"/>
       <c r="K2" s="6">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="L2" s="13"/>
       <c r="M2" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N2" s="6"/>
       <c r="O2" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P2" s="6"/>
       <c r="Q2" s="6">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="R2" s="6"/>
       <c r="S2" s="14"/>
     </row>
-    <row r="3" spans="1:31" ht="126.75" customHeight="1">
+    <row r="3" ht="126.75" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="9">
-        <v>90</v>
+        <v>90.0</v>
       </c>
       <c r="C3" s="10">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>84</v>
@@ -2865,32 +4740,32 @@
       </c>
       <c r="J3" s="9"/>
       <c r="K3" s="9">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="L3" s="15"/>
       <c r="M3" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N3" s="9"/>
       <c r="O3" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P3" s="9"/>
       <c r="Q3" s="9">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="R3" s="9"/>
       <c r="S3" s="16"/>
     </row>
-    <row r="4" spans="1:31" ht="126.75" customHeight="1">
+    <row r="4" ht="126.75" customHeight="1">
       <c r="A4" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="6">
-        <v>94</v>
+        <v>94.0</v>
       </c>
       <c r="C4" s="7">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>86</v>
@@ -2912,32 +4787,32 @@
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L4" s="13"/>
       <c r="M4" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N4" s="6"/>
       <c r="O4" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P4" s="6"/>
       <c r="Q4" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R4" s="6"/>
       <c r="S4" s="14"/>
     </row>
-    <row r="5" spans="1:31" ht="126.75" customHeight="1">
+    <row r="5" ht="126.75" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B5" s="6">
-        <v>95</v>
+        <v>95.0</v>
       </c>
       <c r="C5" s="7">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>88</v>
@@ -2959,34 +4834,34 @@
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="L5" s="13"/>
       <c r="M5" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="P5" s="6"/>
       <c r="Q5" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="R5" s="6"/>
       <c r="S5" s="14">
-        <v>1</v>
+        <v>1.0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="126.75" customHeight="1">
+    <row r="6" ht="126.75" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="6">
-        <v>96</v>
+        <v>96.0</v>
       </c>
       <c r="C6" s="7">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>90</v>
@@ -3008,34 +4883,34 @@
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="L6" s="13"/>
       <c r="M6" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="N6" s="6"/>
       <c r="O6" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="P6" s="6"/>
       <c r="Q6" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="R6" s="6"/>
       <c r="S6" s="14">
-        <v>1</v>
+        <v>1.0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="126.75" customHeight="1">
+    <row r="7" ht="126.75" customHeight="1">
       <c r="A7" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="9">
-        <v>97</v>
+        <v>97.0</v>
       </c>
       <c r="C7" s="10">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>92</v>
@@ -3057,34 +4932,34 @@
       </c>
       <c r="J7" s="9"/>
       <c r="K7" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L7" s="15"/>
       <c r="M7" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N7" s="9"/>
       <c r="O7" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P7" s="9"/>
       <c r="Q7" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R7" s="9"/>
       <c r="S7" s="16">
-        <v>4</v>
+        <v>4.0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="126.75" customHeight="1">
+    <row r="8" ht="126.75" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="9">
-        <v>98</v>
+        <v>98.0</v>
       </c>
       <c r="C8" s="10">
-        <v>7</v>
+        <v>7.0</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>96</v>
@@ -3106,34 +4981,34 @@
       </c>
       <c r="J8" s="9"/>
       <c r="K8" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L8" s="15"/>
       <c r="M8" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N8" s="9"/>
       <c r="O8" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P8" s="9"/>
       <c r="Q8" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R8" s="9"/>
       <c r="S8" s="16">
-        <v>4</v>
+        <v>4.0</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="126.75" customHeight="1">
+    <row r="9" ht="126.75" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="6">
-        <v>99</v>
+        <v>99.0</v>
       </c>
       <c r="C9" s="7">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>99</v>
@@ -3155,34 +5030,34 @@
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L9" s="15"/>
       <c r="M9" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N9" s="9"/>
       <c r="O9" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P9" s="9"/>
       <c r="Q9" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R9" s="9"/>
       <c r="S9" s="16">
-        <v>4</v>
+        <v>4.0</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="126.75" customHeight="1">
+    <row r="10" ht="126.75" customHeight="1">
       <c r="A10" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="6">
-        <v>100</v>
+        <v>100.0</v>
       </c>
       <c r="C10" s="7">
-        <v>9</v>
+        <v>9.0</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>102</v>
@@ -3204,34 +5079,34 @@
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L10" s="15"/>
       <c r="M10" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N10" s="9"/>
       <c r="O10" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P10" s="9"/>
       <c r="Q10" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R10" s="9"/>
       <c r="S10" s="16">
-        <v>4</v>
+        <v>4.0</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="126.75" customHeight="1">
+    <row r="11" ht="126.75" customHeight="1">
       <c r="A11" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="9">
-        <v>101</v>
+        <v>101.0</v>
       </c>
       <c r="C11" s="10">
-        <v>10</v>
+        <v>10.0</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>105</v>
@@ -3253,34 +5128,34 @@
       </c>
       <c r="J11" s="9"/>
       <c r="K11" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L11" s="15"/>
       <c r="M11" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N11" s="9"/>
       <c r="O11" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P11" s="9"/>
       <c r="Q11" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R11" s="9"/>
       <c r="S11" s="16">
-        <v>4</v>
+        <v>4.0</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="126.75" customHeight="1">
+    <row r="12" ht="126.75" customHeight="1">
       <c r="A12" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B12" s="6">
-        <v>102</v>
+        <v>102.0</v>
       </c>
       <c r="C12" s="7">
-        <v>11</v>
+        <v>11.0</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>108</v>
@@ -3302,34 +5177,34 @@
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L12" s="13"/>
       <c r="M12" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N12" s="6"/>
       <c r="O12" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P12" s="6"/>
       <c r="Q12" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="R12" s="6"/>
       <c r="S12" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="126.75" customHeight="1">
+    <row r="13" ht="126.75" customHeight="1">
       <c r="A13" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="9">
-        <v>103</v>
+        <v>103.0</v>
       </c>
       <c r="C13" s="10">
-        <v>12</v>
+        <v>12.0</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>111</v>
@@ -3351,34 +5226,34 @@
       </c>
       <c r="J13" s="9"/>
       <c r="K13" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L13" s="15"/>
       <c r="M13" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N13" s="9"/>
       <c r="O13" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P13" s="9"/>
       <c r="Q13" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R13" s="9"/>
       <c r="S13" s="16">
-        <v>4</v>
+        <v>4.0</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="126.75" customHeight="1">
+    <row r="14" ht="126.75" customHeight="1">
       <c r="A14" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B14" s="9">
-        <v>104</v>
+        <v>104.0</v>
       </c>
       <c r="C14" s="10">
-        <v>13</v>
+        <v>13.0</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>114</v>
@@ -3400,34 +5275,34 @@
       </c>
       <c r="J14" s="9"/>
       <c r="K14" s="9">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="L14" s="15"/>
       <c r="M14" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N14" s="9"/>
       <c r="O14" s="9">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="P14" s="9"/>
       <c r="Q14" s="9">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="R14" s="9"/>
       <c r="S14" s="16">
-        <v>1</v>
+        <v>1.0</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="126.75" customHeight="1">
+    <row r="15" ht="126.75" customHeight="1">
       <c r="A15" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="6">
-        <v>105</v>
+        <v>105.0</v>
       </c>
       <c r="C15" s="7">
-        <v>14</v>
+        <v>14.0</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>117</v>
@@ -3449,34 +5324,34 @@
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N15" s="6"/>
       <c r="O15" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P15" s="6"/>
       <c r="Q15" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R15" s="6"/>
       <c r="S15" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="126.75" customHeight="1">
+    <row r="16" ht="126.75" customHeight="1">
       <c r="A16" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B16" s="6">
-        <v>107</v>
+        <v>107.0</v>
       </c>
       <c r="C16" s="7">
-        <v>15</v>
+        <v>15.0</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>120</v>
@@ -3498,34 +5373,34 @@
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L16" s="13"/>
       <c r="M16" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N16" s="6"/>
       <c r="O16" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P16" s="6"/>
       <c r="Q16" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R16" s="6"/>
       <c r="S16" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="126.75" customHeight="1">
+    <row r="17" ht="126.75" customHeight="1">
       <c r="A17" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="6">
-        <v>108</v>
+        <v>108.0</v>
       </c>
       <c r="C17" s="7">
-        <v>16</v>
+        <v>16.0</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>123</v>
@@ -3547,32 +5422,32 @@
       </c>
       <c r="J17" s="6"/>
       <c r="K17" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L17" s="13"/>
       <c r="M17" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N17" s="6"/>
       <c r="O17" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P17" s="6"/>
       <c r="Q17" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R17" s="6"/>
       <c r="S17" s="14"/>
     </row>
-    <row r="18" spans="1:19" ht="126.75" customHeight="1">
+    <row r="18" ht="126.75" customHeight="1">
       <c r="A18" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="7">
-        <v>17</v>
-      </c>
-      <c r="D18" s="6" t="s">
+        <v>17.0</v>
+      </c>
+      <c r="D18" s="17" t="s">
         <v>126</v>
       </c>
       <c r="E18" s="6"/>
@@ -3588,34 +5463,34 @@
       </c>
       <c r="J18" s="6"/>
       <c r="K18" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L18" s="13"/>
       <c r="M18" s="6">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="N18" s="6"/>
       <c r="O18" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P18" s="6"/>
       <c r="Q18" s="6">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="R18" s="6"/>
       <c r="S18" s="14">
-        <v>3</v>
+        <v>3.0</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="126.75" customHeight="1">
+    <row r="19" ht="126.75" customHeight="1">
       <c r="A19" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="9"/>
       <c r="C19" s="10">
-        <v>18</v>
-      </c>
-      <c r="D19" s="9" t="s">
+        <v>18.0</v>
+      </c>
+      <c r="D19" s="18" t="s">
         <v>129</v>
       </c>
       <c r="E19" s="9"/>
@@ -3631,34 +5506,34 @@
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L19" s="15"/>
       <c r="M19" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N19" s="9"/>
       <c r="O19" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P19" s="9"/>
       <c r="Q19" s="9">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R19" s="9"/>
       <c r="S19" s="16">
-        <v>4</v>
+        <v>4.0</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="126.75" customHeight="1">
+    <row r="20" ht="126.75" customHeight="1">
       <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B20" s="6">
-        <v>193</v>
+        <v>193.0</v>
       </c>
       <c r="C20" s="7">
-        <v>19</v>
+        <v>19.0</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>132</v>
@@ -3680,35 +5555,1022 @@
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L20" s="13"/>
       <c r="M20" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="N20" s="6"/>
       <c r="O20" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P20" s="6"/>
       <c r="Q20" s="6">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R20" s="6"/>
       <c r="S20" s="14"/>
     </row>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AECF4D6-AE40-4555-A16B-BC3C197B36D9}">
-  <sheetPr codeName="Hoja4"/>
-  <dimension ref="A1:AE4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="31" width="10.71"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="43.5" customHeight="1">
+    <row r="1" ht="43.5" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -3779,15 +6641,15 @@
       <c r="AD1" s="5"/>
       <c r="AE1" s="5"/>
     </row>
-    <row r="2" spans="1:31" ht="126.75" customHeight="1">
+    <row r="2" ht="126.75" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B2" s="6">
-        <v>151</v>
+        <v>151.0</v>
       </c>
       <c r="C2" s="7">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>135</v>
@@ -3809,30 +6671,30 @@
       </c>
       <c r="J2" s="6"/>
       <c r="K2" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="L2" s="13"/>
       <c r="M2" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="N2" s="6"/>
       <c r="O2" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="P2" s="6"/>
       <c r="Q2" s="6">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="R2" s="6"/>
       <c r="S2" s="14"/>
     </row>
-    <row r="3" spans="1:31" ht="126.75" customHeight="1">
+    <row r="3" ht="126.75" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="7">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>139</v>
@@ -3852,32 +6714,32 @@
       </c>
       <c r="J3" s="14"/>
       <c r="K3" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L3" s="14"/>
       <c r="M3" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N3" s="14"/>
       <c r="O3" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P3" s="14"/>
       <c r="Q3" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R3" s="14"/>
       <c r="S3" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="126.75" customHeight="1">
+    <row r="4" ht="126.75" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="10">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>139</v>
@@ -3897,40 +6759,1027 @@
       </c>
       <c r="J4" s="16"/>
       <c r="K4" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="L4" s="14"/>
       <c r="M4" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N4" s="14"/>
       <c r="O4" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P4" s="14"/>
       <c r="Q4" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R4" s="14"/>
       <c r="S4" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
     </row>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I4" r:id="rId1" xr:uid="{4298A12E-1B19-4368-8788-4B53AA4F17E5}"/>
+    <hyperlink r:id="rId1" ref="I4"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46B2BDC4-6340-474D-8269-BB04A011B718}">
-  <sheetPr codeName="Hoja5"/>
-  <dimension ref="A1:AE10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="31" width="10.71"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="43.5" customHeight="1">
+    <row r="1" ht="43.5" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4001,15 +7850,15 @@
       <c r="AD1" s="5"/>
       <c r="AE1" s="5"/>
     </row>
-    <row r="2" spans="1:31" ht="126.75" customHeight="1">
+    <row r="2" ht="126.75" customHeight="1">
       <c r="A2" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B2" s="14">
-        <v>153</v>
+        <v>153.0</v>
       </c>
       <c r="C2" s="7">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>145</v>
@@ -4031,30 +7880,30 @@
       </c>
       <c r="J2" s="14"/>
       <c r="K2" s="14">
-        <v>4</v>
-      </c>
-      <c r="L2" s="17"/>
+        <v>4.0</v>
+      </c>
+      <c r="L2" s="19"/>
       <c r="M2" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N2" s="14"/>
       <c r="O2" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P2" s="14"/>
       <c r="Q2" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R2" s="14"/>
       <c r="S2" s="14"/>
     </row>
-    <row r="3" spans="1:31" ht="126.75" customHeight="1">
+    <row r="3" ht="126.75" customHeight="1">
       <c r="A3" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="14"/>
       <c r="C3" s="7">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>149</v>
@@ -4074,32 +7923,32 @@
       </c>
       <c r="J3" s="14"/>
       <c r="K3" s="14">
-        <v>4</v>
-      </c>
-      <c r="L3" s="17"/>
+        <v>4.0</v>
+      </c>
+      <c r="L3" s="19"/>
       <c r="M3" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N3" s="14"/>
       <c r="O3" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P3" s="14"/>
       <c r="Q3" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R3" s="14"/>
       <c r="S3" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="126.75" customHeight="1">
+    <row r="4" ht="126.75" customHeight="1">
       <c r="A4" s="16" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="10">
-        <v>3</v>
+        <v>3.0</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>149</v>
@@ -4114,37 +7963,37 @@
       <c r="H4" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="20" t="s">
         <v>153</v>
       </c>
       <c r="J4" s="16"/>
       <c r="K4" s="14">
-        <v>4</v>
-      </c>
-      <c r="L4" s="17"/>
+        <v>4.0</v>
+      </c>
+      <c r="L4" s="19"/>
       <c r="M4" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N4" s="14"/>
       <c r="O4" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P4" s="14"/>
       <c r="Q4" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R4" s="14"/>
       <c r="S4" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="126.75" customHeight="1">
+    <row r="5" ht="126.75" customHeight="1">
       <c r="A5" s="16" t="s">
         <v>19</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="10">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>154</v>
@@ -4166,32 +8015,32 @@
       </c>
       <c r="J5" s="16"/>
       <c r="K5" s="16">
-        <v>4</v>
-      </c>
-      <c r="L5" s="19"/>
+        <v>4.0</v>
+      </c>
+      <c r="L5" s="21"/>
       <c r="M5" s="16">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N5" s="16"/>
       <c r="O5" s="16">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="16">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R5" s="16"/>
       <c r="S5" s="16">
-        <v>1</v>
+        <v>1.0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="126.75" customHeight="1">
+    <row r="6" ht="126.75" customHeight="1">
       <c r="A6" s="16" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="16"/>
       <c r="C6" s="10">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>154</v>
@@ -4206,40 +8055,40 @@
       <c r="H6" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="20" t="s">
-        <v>167</v>
+      <c r="I6" s="22" t="s">
+        <v>157</v>
       </c>
       <c r="J6" s="16"/>
       <c r="K6" s="16">
-        <v>4</v>
-      </c>
-      <c r="L6" s="19"/>
+        <v>4.0</v>
+      </c>
+      <c r="L6" s="21"/>
       <c r="M6" s="16">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N6" s="16"/>
       <c r="O6" s="16">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P6" s="16"/>
       <c r="Q6" s="16">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R6" s="16"/>
       <c r="S6" s="16">
-        <v>1</v>
+        <v>1.0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="126.75" customHeight="1">
+    <row r="7" ht="126.75" customHeight="1">
       <c r="A7" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="7">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>150</v>
@@ -4248,45 +8097,45 @@
         <v>147</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H7" s="14" t="s">
         <v>40</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J7" s="14"/>
       <c r="K7" s="14">
-        <v>4</v>
-      </c>
-      <c r="L7" s="17"/>
+        <v>4.0</v>
+      </c>
+      <c r="L7" s="19"/>
       <c r="M7" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N7" s="14"/>
       <c r="O7" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P7" s="14"/>
       <c r="Q7" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R7" s="14"/>
       <c r="S7" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="126.75" customHeight="1">
+    <row r="8" ht="126.75" customHeight="1">
       <c r="A8" s="16" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="10">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>150</v>
@@ -4298,40 +8147,40 @@
       <c r="H8" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="I8" s="18" t="s">
-        <v>160</v>
+      <c r="I8" s="20" t="s">
+        <v>161</v>
       </c>
       <c r="J8" s="16"/>
       <c r="K8" s="14">
-        <v>4</v>
-      </c>
-      <c r="L8" s="17"/>
+        <v>4.0</v>
+      </c>
+      <c r="L8" s="19"/>
       <c r="M8" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="N8" s="14"/>
       <c r="O8" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="P8" s="14"/>
       <c r="Q8" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
       <c r="R8" s="14"/>
       <c r="S8" s="14">
-        <v>4</v>
+        <v>4.0</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="126.75" customHeight="1">
+    <row r="9" ht="126.75" customHeight="1">
       <c r="A9" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="14"/>
       <c r="C9" s="7">
-        <v>6</v>
+        <v>6.0</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>150</v>
@@ -4340,56 +8189,56 @@
         <v>147</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H9" s="14" t="s">
         <v>40</v>
       </c>
       <c r="I9" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J9" s="14"/>
       <c r="K9" s="14">
-        <v>1</v>
-      </c>
-      <c r="L9" s="17"/>
+        <v>1.0</v>
+      </c>
+      <c r="L9" s="19"/>
       <c r="M9" s="14">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="N9" s="14"/>
       <c r="O9" s="14">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="P9" s="14"/>
       <c r="Q9" s="14">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="R9" s="14"/>
       <c r="S9" s="14">
-        <v>1</v>
+        <v>1.0</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="126.75" customHeight="1">
+    <row r="10" ht="126.75" customHeight="1">
       <c r="A10" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="14">
-        <v>167</v>
+        <v>167.0</v>
       </c>
       <c r="C10" s="7">
-        <v>8</v>
+        <v>8.0</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F10" s="14" t="s">
         <v>147</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H10" s="14" t="s">
         <v>83</v>
@@ -4399,29 +8248,1012 @@
       </c>
       <c r="J10" s="14"/>
       <c r="K10" s="14">
-        <v>1</v>
-      </c>
-      <c r="L10" s="17"/>
+        <v>1.0</v>
+      </c>
+      <c r="L10" s="19"/>
       <c r="M10" s="14">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="N10" s="14"/>
       <c r="O10" s="14">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="P10" s="14"/>
       <c r="Q10" s="14">
-        <v>1</v>
+        <v>1.0</v>
       </c>
       <c r="R10" s="14"/>
       <c r="S10" s="14"/>
     </row>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I4" r:id="rId1" xr:uid="{C3CB15C0-ADAF-4314-AAA8-052B475ACBD9}"/>
-    <hyperlink ref="I6" r:id="rId2" xr:uid="{0FA4E211-163E-449A-8E20-41653B7ACE72}"/>
-    <hyperlink ref="I8" r:id="rId3" xr:uid="{FB9346D9-CD5B-4C02-8F39-D4445AAE9E16}"/>
+    <hyperlink r:id="rId1" ref="I4"/>
+    <hyperlink r:id="rId2" ref="I6"/>
+    <hyperlink r:id="rId3" ref="I8"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>